--- a/data/trans_camb/IP04D$aparatos-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 6,31</t>
+          <t>-18,88; 6,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 12,17</t>
+          <t>-12,51; 10,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 9,37</t>
+          <t>-14,53; 9,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 8,72</t>
+          <t>-14,68; 8,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 5,89</t>
+          <t>-12,48; 4,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 6,27</t>
+          <t>-11,88; 5,62</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 15,37</t>
+          <t>-33,78; 15,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 27,57</t>
+          <t>-23,02; 26,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 23,78</t>
+          <t>-27,29; 24,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 23,62</t>
+          <t>-28,4; 22,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 13,65</t>
+          <t>-23,7; 10,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 15,13</t>
+          <t>-22,62; 13,17</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 7,36</t>
+          <t>-16,36; 6,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 11,53</t>
+          <t>-11,82; 12,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 5,77</t>
+          <t>-17,67; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 20,69</t>
+          <t>-4,99; 19,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 2,84</t>
+          <t>-13,75; 2,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 12,1</t>
+          <t>-4,51; 12,19</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 13,92</t>
+          <t>-26,35; 12,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 23,38</t>
+          <t>-19,06; 25,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 12,82</t>
+          <t>-33,07; 10,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 48,3</t>
+          <t>-10,09; 46,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 6,19</t>
+          <t>-24,46; 5,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 25,6</t>
+          <t>-7,32; 25,2</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 2,02</t>
+          <t>-23,14; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 10,69</t>
+          <t>-16,59; 10,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,46; -1,43</t>
+          <t>-29,02; -4,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 13,77</t>
+          <t>-16,44; 13,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,14; -4,7</t>
+          <t>-22,54; -4,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 7,85</t>
+          <t>-11,99; 8,71</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 3,36</t>
+          <t>-33,97; 2,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,87; 18,06</t>
+          <t>-23,67; 17,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -3,23</t>
+          <t>-41,63; -7,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 22,8</t>
+          <t>-23,48; 21,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,31; -7,18</t>
+          <t>-32,8; -7,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 12,33</t>
+          <t>-17,19; 14,48</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -11,16</t>
+          <t>-26,49; -10,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 8,41</t>
+          <t>-15,33; 8,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 3,16</t>
+          <t>-13,0; 1,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 6,63</t>
+          <t>-10,04; 6,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,75; -6,91</t>
+          <t>-18,69; -7,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 4,58</t>
+          <t>-9,61; 5,44</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -17,0</t>
+          <t>-36,51; -16,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 12,73</t>
+          <t>-21,39; 12,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 5,36</t>
+          <t>-20,14; 2,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 11,08</t>
+          <t>-15,11; 11,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,2; -10,87</t>
+          <t>-26,89; -11,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 7,39</t>
+          <t>-14,3; 8,8</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 6,83</t>
+          <t>-10,97; 5,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 12,03</t>
+          <t>-7,15; 11,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 4,24</t>
+          <t>-15,22; 3,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 8,79</t>
+          <t>-18,43; 7,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 2,54</t>
+          <t>-10,44; 2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 6,17</t>
+          <t>-10,15; 7,1</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 10,85</t>
+          <t>-15,5; 9,27</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 19,26</t>
+          <t>-10,31; 18,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 6,11</t>
+          <t>-21,04; 6,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 13,69</t>
+          <t>-25,98; 11,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 4,0</t>
+          <t>-15,05; 3,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 9,49</t>
+          <t>-14,67; 11,08</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-38,05; -8,4</t>
+          <t>-37,59; -8,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 10,1</t>
+          <t>-18,33; 9,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,18; -3,68</t>
+          <t>-30,05; -3,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 9,93</t>
+          <t>-16,14; 10,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-29,46; -10,45</t>
+          <t>-29,03; -9,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 6,54</t>
+          <t>-14,07; 5,64</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,45; -12,87</t>
+          <t>-47,71; -13,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 15,83</t>
+          <t>-22,46; 14,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,86; -5,9</t>
+          <t>-38,87; -4,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 15,15</t>
+          <t>-20,85; 16,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -15,34</t>
+          <t>-38,22; -14,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 9,72</t>
+          <t>-18,04; 8,64</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -7,0</t>
+          <t>-16,04; -7,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 4,22</t>
+          <t>-7,11; 3,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -3,65</t>
+          <t>-12,31; -3,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 2,78</t>
+          <t>-6,96; 2,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -6,63</t>
+          <t>-12,79; -6,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,37</t>
+          <t>-5,8; 1,64</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,8; -11,29</t>
+          <t>-23,96; -12,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 6,73</t>
+          <t>-10,72; 5,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,92; -6,24</t>
+          <t>-19,38; -6,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 4,81</t>
+          <t>-11,06; 4,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-20,12; -10,81</t>
+          <t>-19,85; -10,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 2,2</t>
+          <t>-9,2; 2,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 6,62</t>
+          <t>-17,68; 6,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 10,99</t>
+          <t>-12,19; 11,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 9,18</t>
+          <t>-14,15; 10,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 8,76</t>
+          <t>-15,2; 10,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 4,61</t>
+          <t>-12,95; 3,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 5,62</t>
+          <t>-11,32; 6,28</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 15,84</t>
+          <t>-33,32; 14,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 26,68</t>
+          <t>-22,66; 26,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 24,43</t>
+          <t>-27,13; 26,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 22,32</t>
+          <t>-29,13; 25,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 10,98</t>
+          <t>-25,15; 9,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 13,17</t>
+          <t>-21,18; 14,68</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 6,49</t>
+          <t>-17,12; 6,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 12,73</t>
+          <t>-12,0; 11,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 4,49</t>
+          <t>-16,66; 6,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 19,79</t>
+          <t>-5,62; 20,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 2,5</t>
+          <t>-13,76; 2,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 12,19</t>
+          <t>-4,83; 11,99</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 12,12</t>
+          <t>-27,54; 13,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 25,06</t>
+          <t>-19,22; 23,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 10,88</t>
+          <t>-31,28; 15,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 46,61</t>
+          <t>-9,66; 48,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 5,29</t>
+          <t>-24,08; 5,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 25,2</t>
+          <t>-8,6; 24,19</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 1,52</t>
+          <t>-24,06; 0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 10,59</t>
+          <t>-16,89; 9,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-29,02; -4,05</t>
+          <t>-28,28; -2,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 13,23</t>
+          <t>-15,17; 13,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,54; -4,15</t>
+          <t>-23,8; -5,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 8,71</t>
+          <t>-11,53; 8,3</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 2,51</t>
+          <t>-34,04; 1,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 17,66</t>
+          <t>-24,17; 15,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -7,23</t>
+          <t>-40,43; -3,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 21,5</t>
+          <t>-20,93; 22,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,8; -7,53</t>
+          <t>-34,02; -8,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 14,48</t>
+          <t>-16,64; 13,23</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -10,92</t>
+          <t>-26,69; -11,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 8,69</t>
+          <t>-14,43; 9,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 1,83</t>
+          <t>-13,84; 2,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 6,55</t>
+          <t>-10,34; 6,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -7,19</t>
+          <t>-17,83; -6,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 5,44</t>
+          <t>-9,12; 5,35</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,51; -16,7</t>
+          <t>-36,42; -16,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 12,55</t>
+          <t>-20,22; 13,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 2,86</t>
+          <t>-20,9; 3,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 11,03</t>
+          <t>-15,92; 11,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,89; -11,25</t>
+          <t>-25,93; -10,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 8,8</t>
+          <t>-13,37; 8,93</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 5,97</t>
+          <t>-11,83; 7,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 11,59</t>
+          <t>-7,12; 12,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 3,87</t>
+          <t>-15,12; 3,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 7,5</t>
+          <t>-17,3; 7,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 2,03</t>
+          <t>-10,35; 3,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 7,1</t>
+          <t>-10,63; 6,41</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 9,27</t>
+          <t>-16,18; 11,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 18,22</t>
+          <t>-9,75; 19,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 6,26</t>
+          <t>-21,46; 5,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 11,51</t>
+          <t>-24,48; 11,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 3,16</t>
+          <t>-15,0; 4,88</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 11,08</t>
+          <t>-14,88; 9,76</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -8,26</t>
+          <t>-36,62; -7,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,99</t>
+          <t>-18,56; 10,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,05; -3,4</t>
+          <t>-29,64; -2,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 10,75</t>
+          <t>-16,92; 9,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-29,03; -9,59</t>
+          <t>-28,7; -9,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 5,64</t>
+          <t>-13,44; 6,08</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,71; -13,11</t>
+          <t>-46,76; -11,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 14,67</t>
+          <t>-22,88; 16,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,87; -4,93</t>
+          <t>-38,78; -4,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 16,13</t>
+          <t>-21,57; 13,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,22; -14,3</t>
+          <t>-37,87; -13,99</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 8,64</t>
+          <t>-17,0; 9,05</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,04; -7,65</t>
+          <t>-15,72; -7,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,7</t>
+          <t>-6,64; 3,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -3,92</t>
+          <t>-12,39; -3,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 2,76</t>
+          <t>-6,6; 3,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -6,68</t>
+          <t>-12,87; -6,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 1,64</t>
+          <t>-5,47; 1,78</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -12,09</t>
+          <t>-23,71; -11,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 5,79</t>
+          <t>-10,14; 5,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -6,41</t>
+          <t>-19,89; -6,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 4,68</t>
+          <t>-10,6; 5,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -10,96</t>
+          <t>-20,21; -10,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 2,71</t>
+          <t>-8,63; 2,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Clase-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,08</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-5,84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,0</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-0,16</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 6,68</t>
+          <t>-13,87; 9,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 11,49</t>
+          <t>-10,85; 11,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 10,23</t>
+          <t>-17,67; 6,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 10,31</t>
+          <t>-13,65; 10,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 3,97</t>
+          <t>-12,05; 5,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 6,28</t>
+          <t>-8,37; 8,37</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-4,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-11,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,11%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-4,35%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,21%</t>
+          <t>-2,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,33%</t>
+          <t>-0,33%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 14,92</t>
+          <t>-27,25; 23,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 26,57</t>
+          <t>-21,2; 29,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 26,13</t>
+          <t>-31,97; 15,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 25,64</t>
+          <t>-24,71; 26,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 9,32</t>
+          <t>-23,32; 13,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 14,68</t>
+          <t>-16,05; 20,02</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,46</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-5,21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,96</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 6,73</t>
+          <t>-16,6; 5,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 11,91</t>
+          <t>-4,12; 21,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 6,08</t>
+          <t>-16,4; 7,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 20,17</t>
+          <t>-11,06; 12,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 2,75</t>
+          <t>-13,19; 2,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 11,99</t>
+          <t>-4,12; 12,8</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-12,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-9,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,09%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-12,17%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 13,04</t>
+          <t>-31,16; 12,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 23,66</t>
+          <t>-7,0; 50,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 15,0</t>
+          <t>-26,15; 13,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 48,86</t>
+          <t>-17,76; 23,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 5,76</t>
+          <t>-23,56; 6,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 24,19</t>
+          <t>-7,37; 26,47</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-16,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-11,82</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-16,45</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>0,13</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 0,77</t>
+          <t>-28,46; -1,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 9,76</t>
+          <t>-10,14; 15,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,28; -2,1</t>
+          <t>-24,49; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 13,33</t>
+          <t>-15,63; 11,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,8; -5,47</t>
+          <t>-23,14; -4,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 8,3</t>
+          <t>-9,05; 9,46</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-24,95%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-17,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,19%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-24,95%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,68%</t>
+          <t>-2,11%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,25%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 1,57</t>
+          <t>-40,68; -3,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 15,97</t>
+          <t>-14,24; 26,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,43; -3,93</t>
+          <t>-35,48; 3,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 22,95</t>
+          <t>-21,73; 19,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,02; -8,52</t>
+          <t>-33,31; -7,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 13,23</t>
+          <t>-12,85; 14,94</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-18,92</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-4,58</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-5,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-3,69</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -11,17</t>
+          <t>-13,85; 3,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 9,05</t>
+          <t>-9,58; 6,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 2,12</t>
+          <t>-25,8; -11,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 6,9</t>
+          <t>-14,09; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,83; -6,85</t>
+          <t>-17,75; -6,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 5,35</t>
+          <t>-9,13; 2,16</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-9,18%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-2,64%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-27,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-6,6%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-9,18%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,5%</t>
+          <t>-8,53%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,41%</t>
+          <t>-5,62%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,42; -16,85</t>
+          <t>-20,89; 5,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 13,7</t>
+          <t>-14,96; 11,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 3,63</t>
+          <t>-35,64; -17,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 11,33</t>
+          <t>-19,13; 2,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,93; -10,89</t>
+          <t>-26,2; -10,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 8,93</t>
+          <t>-13,53; 3,33</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-5,47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-2,55</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-5,47</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,11</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 7,36</t>
+          <t>-15,06; 4,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 12,07</t>
+          <t>-14,54; 10,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 3,6</t>
+          <t>-12,11; 6,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 7,31</t>
+          <t>-7,4; 11,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 3,1</t>
+          <t>-10,19; 2,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 6,41</t>
+          <t>-8,35; 7,12</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-8,11%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-2,22%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-3,78%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-8,11%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-4,61%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,17%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 11,97</t>
+          <t>-20,93; 6,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 19,45</t>
+          <t>-20,16; 15,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 5,45</t>
+          <t>-17,22; 10,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 11,0</t>
+          <t>-10,4; 18,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 4,88</t>
+          <t>-14,47; 4,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 9,76</t>
+          <t>-11,97; 10,87</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-16,57</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,97</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-23,5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-4,38</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-16,57</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3,18</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-36,62; -7,59</t>
+          <t>-29,18; -3,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 10,73</t>
+          <t>-15,93; 11,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,64; -2,88</t>
+          <t>-38,05; -8,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 9,19</t>
+          <t>-17,88; 10,8</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-28,7; -9,65</t>
+          <t>-29,46; -10,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 6,08</t>
+          <t>-11,89; 8,05</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-22,82%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-2,71%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-31,95%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-5,96%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-22,82%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-4,38%</t>
+          <t>-4,17%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-3,35%</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,76; -11,45</t>
+          <t>-38,86; -5,9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,88; 16,58</t>
+          <t>-21,08; 16,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,78; -4,61</t>
+          <t>-48,45; -12,87</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 13,94</t>
+          <t>-22,19; 16,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,87; -13,99</t>
+          <t>-39,07; -15,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 9,05</t>
+          <t>-15,39; 11,54</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-8,03</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-11,45</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-8,03</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-1,36</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -7,24</t>
+          <t>-11,84; -3,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 3,58</t>
+          <t>-5,27; 4,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,39; -3,74</t>
+          <t>-15,77; -7,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 3,18</t>
+          <t>-6,49; 2,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -6,73</t>
+          <t>-12,79; -6,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,78</t>
+          <t>-4,71; 1,69</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-13,17%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-0,71%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-17,78%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-3,3%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-13,17%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-3,12%</t>
+          <t>-3,56%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-3,3%</t>
+          <t>-2,16%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -11,45</t>
+          <t>-18,92; -6,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 5,79</t>
+          <t>-8,32; 7,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,89; -6,33</t>
+          <t>-23,8; -11,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 5,41</t>
+          <t>-10,1; 3,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-20,21; -10,95</t>
+          <t>-20,12; -10,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 2,82</t>
+          <t>-7,36; 2,75</t>
         </is>
       </c>
     </row>
